--- a/docs/harness/wirelist/AntiTheft-wirelist.xlsx
+++ b/docs/harness/wirelist/AntiTheft-wirelist.xlsx
@@ -1202,10 +1202,14 @@
       <c r="AB3" s="37" t="inlineStr"/>
       <c r="AC3" s="38" t="inlineStr"/>
       <c r="AD3" s="38" t="inlineStr"/>
-      <c r="AE3" s="38" t="inlineStr"/>
+      <c r="AE3" s="38" t="inlineStr">
+        <is>
+          <t>end t_at_gnd: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_at_gnd (Cabin ground stud near the alarm (spot and EWD ID TBD, M6)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG3" s="38" t="inlineStr"/>
@@ -1416,10 +1420,14 @@
       <c r="AB5" s="37" t="inlineStr"/>
       <c r="AC5" s="38" t="inlineStr"/>
       <c r="AD5" s="38" t="inlineStr"/>
-      <c r="AE5" s="38" t="inlineStr"/>
+      <c r="AE5" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_park: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF5" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_park is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG5" s="38" t="inlineStr"/>
@@ -1856,10 +1864,14 @@
       <c r="AB9" s="37" t="inlineStr"/>
       <c r="AC9" s="38" t="inlineStr"/>
       <c r="AD9" s="38" t="inlineStr"/>
-      <c r="AE9" s="38" t="inlineStr"/>
+      <c r="AE9" s="38" t="inlineStr">
+        <is>
+          <t>end t_at_gnd_b: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF9" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_at_gnd_b (Cabin ground stud near the alarm (spot and EWD ID TBD, M6)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG9" s="38" t="inlineStr"/>
@@ -1963,10 +1975,14 @@
       <c r="AB10" s="53" t="inlineStr"/>
       <c r="AC10" s="54" t="inlineStr"/>
       <c r="AD10" s="54" t="inlineStr"/>
-      <c r="AE10" s="54" t="inlineStr"/>
+      <c r="AE10" s="54" t="inlineStr">
+        <is>
+          <t>end t_at_gnd_b: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF10" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_at_gnd_b (Cabin ground stud near the alarm (spot and EWD ID TBD, M6)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG10" s="54" t="inlineStr"/>
@@ -2177,10 +2193,14 @@
       <c r="AB12" s="53" t="inlineStr"/>
       <c r="AC12" s="54" t="inlineStr"/>
       <c r="AD12" s="54" t="inlineStr"/>
-      <c r="AE12" s="54" t="inlineStr"/>
+      <c r="AE12" s="54" t="inlineStr">
+        <is>
+          <t>end t_at_gnd: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF12" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_at_gnd (Cabin ground stud near the alarm (spot and EWD ID TBD, M6)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG12" s="54" t="inlineStr"/>
@@ -2282,10 +2302,14 @@
       <c r="AB13" s="37" t="inlineStr"/>
       <c r="AC13" s="38" t="inlineStr"/>
       <c r="AD13" s="38" t="inlineStr"/>
-      <c r="AE13" s="38" t="inlineStr"/>
+      <c r="AE13" s="38" t="inlineStr">
+        <is>
+          <t>end t_at_gnd_c: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF13" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_at_gnd_c (Cabin ground stud near the alarm (spot and EWD ID TBD, M6)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG13" s="38" t="inlineStr"/>
@@ -2391,10 +2415,14 @@
       <c r="AB14" s="53" t="inlineStr"/>
       <c r="AC14" s="54" t="inlineStr"/>
       <c r="AD14" s="54" t="inlineStr"/>
-      <c r="AE14" s="54" t="inlineStr"/>
+      <c r="AE14" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_12v_shk: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF14" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_12v_shk is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG14" s="54" t="inlineStr"/>
@@ -2498,10 +2526,14 @@
       <c r="AB15" s="37" t="inlineStr"/>
       <c r="AC15" s="38" t="inlineStr"/>
       <c r="AD15" s="38" t="inlineStr"/>
-      <c r="AE15" s="38" t="inlineStr"/>
+      <c r="AE15" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_at_12v: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF15" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_at_12v is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG15" s="38" t="inlineStr"/>
@@ -2605,10 +2637,14 @@
       <c r="AB16" s="53" t="inlineStr"/>
       <c r="AC16" s="54" t="inlineStr"/>
       <c r="AD16" s="54" t="inlineStr"/>
-      <c r="AE16" s="54" t="inlineStr"/>
+      <c r="AE16" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_door: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF16" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_door is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG16" s="54" t="inlineStr"/>
@@ -2712,10 +2748,14 @@
       <c r="AB17" s="37" t="inlineStr"/>
       <c r="AC17" s="38" t="inlineStr"/>
       <c r="AD17" s="38" t="inlineStr"/>
-      <c r="AE17" s="38" t="inlineStr"/>
+      <c r="AE17" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_hood: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF17" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_hood is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG17" s="38" t="inlineStr"/>
@@ -2819,10 +2859,14 @@
       <c r="AB18" s="53" t="inlineStr"/>
       <c r="AC18" s="54" t="inlineStr"/>
       <c r="AD18" s="54" t="inlineStr"/>
-      <c r="AE18" s="54" t="inlineStr"/>
+      <c r="AE18" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_ig: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF18" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_ig is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG18" s="54" t="inlineStr"/>
@@ -2924,10 +2968,14 @@
       <c r="AB19" s="37" t="inlineStr"/>
       <c r="AC19" s="38" t="inlineStr"/>
       <c r="AD19" s="38" t="inlineStr"/>
-      <c r="AE19" s="38" t="inlineStr"/>
+      <c r="AE19" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_park: node of the wire list (SoT); end t_at_park: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF19" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_park is not named in the SoT (drawing only); end t_at_park (Park lamp flash relay lead (cabin relay, part and spot TBD)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG19" s="38" t="inlineStr"/>
@@ -3031,10 +3079,14 @@
       <c r="AB20" s="53" t="inlineStr"/>
       <c r="AC20" s="54" t="inlineStr"/>
       <c r="AD20" s="54" t="inlineStr"/>
-      <c r="AE20" s="54" t="inlineStr"/>
+      <c r="AE20" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_trunk: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF20" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_trunk is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG20" s="54" t="inlineStr"/>
@@ -3136,10 +3188,14 @@
       <c r="AB21" s="37" t="inlineStr"/>
       <c r="AC21" s="38" t="inlineStr"/>
       <c r="AD21" s="38" t="inlineStr"/>
-      <c r="AE21" s="38" t="inlineStr"/>
+      <c r="AE21" s="38" t="inlineStr">
+        <is>
+          <t>end t_at_door: end row of the wire list (SoT); splice sp_door: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF21" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_at_door (OEM door courtesy switch lead (tap spot and EWD page TBD)) is drawing-only: not named in the SoT; splice sp_door is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG21" s="38" t="inlineStr"/>
@@ -3241,10 +3297,14 @@
       <c r="AB22" s="53" t="inlineStr"/>
       <c r="AC22" s="54" t="inlineStr"/>
       <c r="AD22" s="54" t="inlineStr"/>
-      <c r="AE22" s="54" t="inlineStr"/>
+      <c r="AE22" s="54" t="inlineStr">
+        <is>
+          <t>end t_at_hood: end row of the wire list (SoT); splice sp_hood: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF22" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_at_hood (Hood pin switch lead (new switch, RH front via loom C, spot TBD)) is drawing-only: not named in the SoT; splice sp_hood is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG22" s="54" t="inlineStr"/>
@@ -3346,10 +3406,14 @@
       <c r="AB23" s="37" t="inlineStr"/>
       <c r="AC23" s="38" t="inlineStr"/>
       <c r="AD23" s="38" t="inlineStr"/>
-      <c r="AE23" s="38" t="inlineStr"/>
+      <c r="AE23" s="38" t="inlineStr">
+        <is>
+          <t>end t_at_trunk: end row of the wire list (SoT); splice sp_trunk: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF23" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_at_trunk (Trunk pin switch lead (new switch, spot TBD)) is drawing-only: not named in the SoT; splice sp_trunk is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG23" s="38" t="inlineStr"/>
@@ -3560,7 +3624,7 @@
       </c>
       <c r="L3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3680,7 @@
       </c>
       <c r="L4" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3736,7 @@
       </c>
       <c r="L5" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3792,7 @@
       </c>
       <c r="L6" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3848,7 @@
       </c>
       <c r="L7" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3904,7 @@
       </c>
       <c r="L8" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3960,7 @@
       </c>
       <c r="L9" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/AntiTheft-wirelist.xlsx
+++ b/docs/harness/wirelist/AntiTheft-wirelist.xlsx
@@ -2386,7 +2386,7 @@
       </c>
       <c r="R14" s="47" t="inlineStr">
         <is>
-          <t>+12V ALMS 2A (LOGIC BUS1-8)</t>
+          <t>+12V Shock sensor +12 V (LOGIC BUS1-8)</t>
         </is>
       </c>
       <c r="S14" s="48" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="R15" s="31" t="inlineStr">
         <is>
-          <t>+12V ALM 5A (LOGIC BUS1-7)</t>
+          <t>+12V Alarm +12 V (LOGIC BUS1-7)</t>
         </is>
       </c>
       <c r="S15" s="32" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="R18" s="47" t="inlineStr">
         <is>
-          <t>+12V ALMIG 2A (LOGIC BUS2-9)</t>
+          <t>+12V Alarm ignition +12V (LOGIC BUS2-9)</t>
         </is>
       </c>
       <c r="S18" s="48" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="E3" s="31" t="inlineStr">
         <is>
-          <t>+12V ALM 5A (LOGIC BUS1-7)</t>
+          <t>+12V Alarm +12 V (LOGIC BUS1-7)</t>
         </is>
       </c>
       <c r="F3" s="32" t="n">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="E4" s="47" t="inlineStr">
         <is>
-          <t>+12V ALMIG 2A (LOGIC BUS2-9)</t>
+          <t>+12V Alarm ignition +12V (LOGIC BUS2-9)</t>
         </is>
       </c>
       <c r="F4" s="48" t="n">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="E9" s="31" t="inlineStr">
         <is>
-          <t>+12V ALMS 2A (LOGIC BUS1-8)</t>
+          <t>+12V Shock sensor +12 V (LOGIC BUS1-8)</t>
         </is>
       </c>
       <c r="F9" s="32" t="n">

--- a/docs/harness/wirelist/AntiTheft-wirelist.xlsx
+++ b/docs/harness/wirelist/AntiTheft-wirelist.xlsx
@@ -1296,7 +1296,7 @@
       </c>
       <c r="V4" s="50" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W4" s="50" t="inlineStr"/>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="V6" s="50" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W6" s="50" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="V7" s="34" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W7" s="34" t="inlineStr"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="V8" s="50" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W8" s="50" t="inlineStr"/>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="V11" s="34" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W11" s="34" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="V16" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W16" s="50" t="inlineStr"/>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="V17" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W17" s="34" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="V18" s="50" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W18" s="50" t="inlineStr"/>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="V20" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W20" s="50" t="inlineStr"/>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="V21" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W21" s="34" t="inlineStr"/>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="V22" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W22" s="50" t="inlineStr"/>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="V23" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W23" s="34" t="inlineStr"/>

--- a/docs/harness/wirelist/AntiTheft-wirelist.xlsx
+++ b/docs/harness/wirelist/AntiTheft-wirelist.xlsx
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D8" s="39" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E8" s="40" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AG8" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_at_immob2_bc on B-cabin, 120 mm; w_at_immob2 on AntiTheft, 1210 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_at_immob2_bc on ECU-cabin, 120 mm; w_at_immob2 on AntiTheft, 1210 mm)</t>
         </is>
       </c>
     </row>
